--- a/data/trans_dic/P41D_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Provincia-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -582,14 +582,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -622,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -672,24 +672,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -722,24 +722,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaén</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -822,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 82,3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -872,24 +872,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0; 56,93</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,15</t>
+          <t>0,0; 76,95</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -922,83 +922,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>0,0; 43,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>9,28; 59,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,95</t>
+          <t>7,36; 41,91</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 45,62</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>8,55; 60,85</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>7,31; 41,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A20:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
@@ -1016,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1029,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1078,7 +1027,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1093,12 +1042,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1142</t>
         </is>
       </c>
     </row>
@@ -1144,14 +1093,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2595</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1166,12 +1115,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1138,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1207,24 +1156,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1121</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>261; 1141</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2595</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1280,24 +1229,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 931</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 936</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1201</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1353,24 +1302,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2483</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 934</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2175</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1385,12 +1334,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>783</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>783</t>
         </is>
       </c>
     </row>
@@ -1426,24 +1375,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 535</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 449</t>
+          <t>0; 1416</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 726</t>
+          <t>0; 1416</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Jaén</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1453,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>1307</t>
         </is>
       </c>
     </row>
@@ -1499,24 +1448,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3532</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1416</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1416</t>
+          <t>0; 4373</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1526,17 +1475,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1646</t>
         </is>
       </c>
     </row>
@@ -1572,24 +1521,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3532</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1014</t>
+          <t>0; 2875</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4418</t>
+          <t>0; 3798</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1599,17 +1548,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>4879</t>
         </is>
       </c>
     </row>
@@ -1645,108 +1594,34 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1173</t>
+          <t>0; 5732</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2875</t>
+          <t>1071; 6917</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3798</t>
+          <t>1830; 10417</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>3571</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>0; 6071</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>986; 7024</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1816; 10213</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>

--- a/data/trans_dic/P41D_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Provincia-trans_dic.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,3</t>
+          <t>0,0; 83,55</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,95</t>
+          <t>0,0; 76,51</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,08</t>
+          <t>0,0; 41,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,28; 59,91</t>
+          <t>8,52; 61,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 41,91</t>
+          <t>6,77; 40,57</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1093</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2595</t>
+          <t>0; 2550</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>771</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>771</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1416</t>
+          <t>0; 1419</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1416</t>
+          <t>0; 1419</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3532</t>
+          <t>0; 3512</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4373</t>
+          <t>0; 4442</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1767</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2875</t>
+          <t>0; 3120</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3798</t>
+          <t>0; 4163</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 5855</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1071; 6917</t>
+          <t>1012; 7250</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1830; 10417</t>
+          <t>1765; 10568</t>
         </is>
       </c>
     </row>
